--- a/output/第10期計画_見込量の季節性の検証と施策反映の設計.xlsx
+++ b/output/第10期計画_見込量の季節性の検証と施策反映の設計.xlsx
@@ -3063,7 +3063,7 @@
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>20.4％（98票中20票）</t>
+          <t>20.2％（99票中20票）</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
@@ -3073,7 +3073,7 @@
       </c>
       <c r="F26" s="6" t="inlineStr">
         <is>
-          <t>目標が未確定。分母が98票と小さい</t>
+          <t>目標が未確定。分母が99票と小さい</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_見込量の季節性の検証と施策反映の設計.xlsx
+++ b/output/第10期計画_見込量の季節性の検証と施策反映の設計.xlsx
@@ -644,7 +644,7 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>令和8年度は令和8年4月から7月までの4か月と確定しました。介護保険事業状況報告の月報（data_nenpo.GEPPO）が4か月分を収録しています。使いづらい主因は季節ではなく単価です。給付費は令和7年度の36.00％で4.320か月相当ですが、数量は月報で+1.99％にとどまり期待は4.079か月相当です。残差は単価であり、分母の採り方で+1.63％から+5.90％の幅があります。</t>
+          <t>令和8年度は令和8年4月から7月までの4か月と確定しました。介護保険事業状況報告の月報（data_nenpo.GEPPO）が4か月分を収録しています。使いづらい主因は季節ではなく単価です。給付費は令和7年度の34.55％で4.146か月相当ですが、数量は月報で+1.99％にとどまり期待は4.079か月相当です。残差は単価であり、分母の採り方で+1.63％から+1.63％の幅があります。</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
@@ -789,7 +789,7 @@
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>①令和8年度の月数は月報により4か月と確定しました（当初は給付費の比から約4.3か月と推計していました）。②単価の残差は確認事項No.87の未解決により＋1.63％から＋5.90％の幅があります（当初は＋5.90％と単一の値で示していました）。③居住系の季節性は測定できません（当初は有意としていました）。</t>
+          <t>①令和8年度の月数は月報により4か月と確定しました（当初は給付費の比から約4.3か月と推計していました）。②単価の残差は＋1.63％です（当初は＋5.90％としていました。確認事項No.87の決着により分母が一つに定まりました）。③居住系の季節性は測定できません（当初は有意としていました）。</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>0.3600</t>
+          <t>0.3455</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
@@ -1863,7 +1863,7 @@
       <c r="E8" s="6" t="inlineStr"/>
       <c r="F8" s="6" t="inlineStr">
         <is>
-          <t>12を乗じると4.320か月相当。月数4か月と一致しない</t>
+          <t>12を乗じると4.146か月相当。月数4か月と一致しない</t>
         </is>
       </c>
     </row>
@@ -1979,7 +1979,7 @@
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>3　残差＝単価（分母の採り方で変わる）</t>
+          <t>3　残差＝単価</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
     <row r="18" ht="24" customHeight="1">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>計画作成支援ツール 3町合計単位</t>
+          <t>給付費データ 広域連合単位</t>
         </is>
       </c>
       <c r="B18" s="5" t="n">
@@ -2044,34 +2044,34 @@
     <row r="19" ht="24" customHeight="1">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>計画作成支援ツール 広域連合単位</t>
+          <t>給付費データ 3町のファイルの合計</t>
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>0.36</v>
+        <v>0.3455</v>
       </c>
       <c r="C19" s="5" t="n">
-        <v>4.32</v>
+        <v>4.146</v>
       </c>
       <c r="D19" s="5" t="n">
         <v>4.079</v>
       </c>
       <c r="E19" s="13" t="inlineStr">
         <is>
-          <t>+5.90％</t>
+          <t>+1.63％</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr">
         <is>
-          <t>+358円</t>
+          <t>+99円</t>
         </is>
       </c>
     </row>
     <row r="20" ht="76" customHeight="1">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>注1）令和8年度は3町合計と広域連合単位が完全に一致します（差0円）。令和7年度のみ4.20％の差があります（確認事項No.87）。したがって同じ基準で比べるには令和7年度も3町合計を用いる必要がありますが、保険料の算定は保険者単位で行うため広域連合単位を用います。この二律背反により残差は確定できません。
-注2）残差が単価であることは、1人1月あたり給付費の令和8年度÷令和7年度（給付費で加重）が1.0590であることと符合します。
+          <t>注1）3町のファイルの合計と広域連合単位のファイルは、令和6年度から令和8年度まで円単位で一致します（差0円）。令和7年度にあった129,580,267円の差は、令和8年9月25日に再提供を受けたファイルにより解消しました（確認事項No.87）。分母はどちらに採っても同じであり、残差は+1.63％の一つの値に定まりました。
+注2）残差が単価であることは、1人1月あたり給付費の令和8年度÷令和7年度（給付費で加重）が1.0163であることと符合します。
 注3）月額への効きは、採用パターンP3の給付費9020.2百万円に残差を乗じて算定しました。</t>
         </is>
       </c>
@@ -2170,18 +2170,18 @@
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>+1.63％〜+5.90％</t>
+          <t>+1.63％</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>確定できない</t>
+          <t>測定できる</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr"/>
       <c r="F26" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.87の解決を要する</t>
+          <t>確認事項No.87の決着により分母が一つに定まった</t>
         </is>
       </c>
     </row>
@@ -2340,7 +2340,7 @@
       </c>
       <c r="F6" s="6" t="inlineStr">
         <is>
-          <t>季節を無視するため、施設を過小に在宅を過大に認識する。また単価の残差（+1.63％〜+5.90％）を年度の水準として固定してしまう。</t>
+          <t>季節を無視するため、施設を過小に在宅を過大に認識する。また単価の残差（+1.63％〜+1.63％）を年度の水準として固定してしまう。</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -4471,7 +4471,7 @@
       </c>
       <c r="F6" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.87。町をまたぐ計上の重複を含む</t>
+          <t>利用者数において広域連合単位と大きく異なる。給付費は一致する</t>
         </is>
       </c>
     </row>
@@ -4481,21 +4481,21 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>★単価を令和8年度の水準に置く（分母＝広域連合）</t>
+          <t>★現行の置き方（見える化の自然体推計×案C補正）</t>
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>9552.299999999999</v>
+        <v>9483.5</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>6787</v>
+        <v>6740</v>
       </c>
       <c r="E7" s="15" t="n">
-        <v>358</v>
+        <v>312</v>
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>残差+5.90％。確認事項No.87の解決を要する</t>
+          <t>パターンP1</t>
         </is>
       </c>
     </row>
@@ -4505,21 +4505,21 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>★現行の置き方（見える化の自然体推計×案C補正）</t>
+          <t>★第1号被保険者負担割合を24％にする</t>
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>9483.5</v>
+        <v>9020.200000000001</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>6740</v>
+        <v>6739</v>
       </c>
       <c r="E8" s="15" t="n">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="F8" s="6" t="inlineStr">
         <is>
-          <t>パターンP1</t>
+          <t>政令による</t>
         </is>
       </c>
     </row>
@@ -4529,21 +4529,21 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>★第1号被保険者負担割合を24％にする</t>
+          <t>★基金を1億円取り崩す</t>
         </is>
       </c>
       <c r="C9" s="5" t="n">
         <v>9020.200000000001</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>6739</v>
+        <v>6120</v>
       </c>
       <c r="E9" s="15" t="n">
-        <v>311</v>
+        <v>-308</v>
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
-          <t>政令による</t>
+          <t>条例第5条第3項</t>
         </is>
       </c>
     </row>
@@ -4553,21 +4553,21 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>★基金を1億円取り崩す</t>
+          <t>★認定者数シナリオを③令和元年水準へ回帰に変える</t>
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>9020.200000000001</v>
+        <v>9382.4</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>6120</v>
+        <v>6672</v>
       </c>
       <c r="E10" s="15" t="n">
-        <v>-308</v>
+        <v>244</v>
       </c>
       <c r="F10" s="6" t="inlineStr">
         <is>
-          <t>条例第5条第3項</t>
+          <t>パターンP5</t>
         </is>
       </c>
     </row>
@@ -4577,21 +4577,21 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>★認定者数シナリオを③令和元年水準へ回帰に変える</t>
+          <t>★基準年度を令和6年度に変える</t>
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>9382.4</v>
+        <v>8716.700000000001</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>6672</v>
+        <v>6224</v>
       </c>
       <c r="E11" s="15" t="n">
-        <v>244</v>
+        <v>-204</v>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>パターンP5</t>
+          <t>パターンP6</t>
         </is>
       </c>
     </row>
@@ -4601,21 +4601,21 @@
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>★基準年度を令和6年度に変える</t>
+          <t>★施策反映で認定者数を2％抑制（H01・H02）</t>
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>8716.700000000001</v>
+        <v>8839.799999999999</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>6224</v>
+        <v>6307</v>
       </c>
       <c r="E12" s="15" t="n">
-        <v>-204</v>
+        <v>-121</v>
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
-          <t>パターンP6</t>
+          <t>目標の達成を前提とする。歯止めを要する</t>
         </is>
       </c>
     </row>
@@ -4625,21 +4625,21 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>★施策反映で認定者数を2％抑制（H01・H02）</t>
+          <t>・単価を令和8年度の水準に置く</t>
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>8839.799999999999</v>
+        <v>9167.1</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>6307</v>
-      </c>
-      <c r="E13" s="15" t="n">
-        <v>-121</v>
+        <v>6527</v>
+      </c>
+      <c r="E13" s="16" t="n">
+        <v>99</v>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>目標の達成を前提とする。歯止めを要する</t>
+          <t>残差+1.63％</t>
         </is>
       </c>
     </row>
@@ -4649,21 +4649,21 @@
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>・単価を令和8年度の水準に置く（分母＝3町合計）</t>
+          <t>・施策反映で認定者数を1％抑制</t>
         </is>
       </c>
       <c r="C14" s="5" t="n">
-        <v>9167.1</v>
+        <v>8930</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>6527</v>
+        <v>6368</v>
       </c>
       <c r="E14" s="16" t="n">
-        <v>99</v>
+        <v>-61</v>
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
-          <t>残差+1.63％</t>
+          <t>同上</t>
         </is>
       </c>
     </row>
@@ -4673,21 +4673,21 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>・施策反映で認定者数を1％抑制</t>
+          <t xml:space="preserve">　定期巡回を5.0人／月整備（純増・令和10年度から）</t>
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>8930</v>
+        <v>9052.799999999999</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>6368</v>
-      </c>
-      <c r="E15" s="16" t="n">
-        <v>-61</v>
+        <v>6450</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>22</v>
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>同上</t>
+          <t>04シート3</t>
         </is>
       </c>
     </row>
@@ -4697,21 +4697,21 @@
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">　定期巡回を5.0人／月整備（純増・令和10年度から）</t>
+          <t xml:space="preserve">　季節指数で年度換算（令和8年度を使う場合のみ）</t>
         </is>
       </c>
       <c r="C16" s="5" t="n">
-        <v>9052.799999999999</v>
+        <v>9000.700000000001</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>6450</v>
+        <v>6415</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>22</v>
+        <v>-13</v>
       </c>
       <c r="F16" s="6" t="inlineStr">
         <is>
-          <t>04シート3</t>
+          <t>P3を採る限り生じない</t>
         </is>
       </c>
     </row>
@@ -4721,21 +4721,21 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">　季節指数で年度換算（令和8年度を使う場合のみ）</t>
+          <t xml:space="preserve">　定期巡回を5.0人／月整備（訪問介護から振替）</t>
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>9000.700000000001</v>
+        <v>9036.700000000001</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>6415</v>
+        <v>6439</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>-13</v>
+        <v>11</v>
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>P3を採る限り生じない</t>
+          <t>04シート3</t>
         </is>
       </c>
     </row>
@@ -4745,62 +4745,38 @@
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">　定期巡回を5.0人／月整備（訪問介護から振替）</t>
+          <t xml:space="preserve">　季節補正（採用パターンP3の場合）</t>
         </is>
       </c>
       <c r="C18" s="5" t="n">
-        <v>9036.700000000001</v>
+        <v>9020.200000000001</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>6439</v>
+        <v>6428</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="F18" s="6" t="inlineStr">
         <is>
-          <t>04シート3</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="30" customHeight="1">
-      <c r="A19" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="B19" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　季節補正（採用パターンP3の場合）</t>
-        </is>
-      </c>
-      <c r="C19" s="5" t="n">
-        <v>9020.200000000001</v>
-      </c>
-      <c r="D19" s="5" t="n">
-        <v>6428</v>
-      </c>
-      <c r="E19" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" s="6" t="inlineStr">
-        <is>
           <t>完結年度は季節指数の和が12となり、換算係数1.0000で恒等的に消える</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="72" customHeight="1">
-      <c r="A21" s="7" t="inlineStr">
-        <is>
-          <t>注1）★は月額100円超（意思決定に効く）で9件、・は50〜100円で2件、無印は50円未満（誤差の範囲）で4件です。
+    <row r="20" ht="72" customHeight="1">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>注1）★は月額100円超（意思決定に効く）で8件、・は50〜100円で2件、無印は50円未満（誤差の範囲）で4件です。
 注2）給付費1％あたりの月額は60.7円です。
 注3）季節補正と施策反映は、いずれも基準年度・出所の選択より小さい位置にあります。ご指示の主訴に対する答えは、「補正を要しない置き方（令和7年度基準）を既に採っている」ことになります。
-注4）単価を令和8年度の水準に置く場合の効きは、分母の採り方により+99円から+358円の幅があります。確認事項No.87の解決が要ります。</t>
+注4）単価を令和8年度の水準に置く場合の効きは+99円です。確認事項No.87の決着により分母が一つに定まりました。</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A20:F20"/>
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A21:F21"/>
     <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5020,17 +4996,17 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>令和8年度は3町合計と広域連合単位が一致し、令和7年度のみ差があること</t>
+          <t>3町合計と広域連合単位の給付費がいずれの年度も一致すること</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>R6 0円／R7 129,580,267円／R8 0円</t>
+          <t>R6 0円／R7 0円／R8 0円</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>令和7年度のみ4.20％の差</t>
+          <t>3か年とも円単位で一致（確認事項No.87は解決）</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
@@ -5045,17 +5021,17 @@
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>単価の残差が分母の採り方で変わること（単一の値で断定していないこと）</t>
+          <t>単価の残差が分母の採り方によらず一つに定まること</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>分母3町合計 +1.63％／分母広域連合 +5.90％</t>
+          <t>分母3町合計 +1.63％／分母広域連合 +1.63％</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>幅は4.27％ポイント</t>
+          <t>差は0.0000％ポイント</t>
         </is>
       </c>
       <c r="E12" s="8" t="inlineStr">
@@ -5245,12 +5221,12 @@
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>分母の採り方により＋1.63％から＋5.90％の幅がある</t>
+          <t>＋1.63％である</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>令和8年度は3町合計と広域連合単位が一致するが、令和7年度のみ4.20％の差がある（確認事項No.87）</t>
+          <t>令和8年9月25日に再提供を受けた給付費データにより令和7年度の差が解消し、分母が一つに定まった（確認事項No.87）</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr"/>
@@ -5417,12 +5393,12 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.87（令和7年度のみ3町合計と広域連合単位が4.20％違うこと）の解決</t>
+          <t>第10期の単価をどの水準に置くか</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>令和8年度の単価の残差が、分母を令和7年度の3町合計に採ると＋1.63％、広域連合単位に採ると＋5.90％となり確定できない。月額に直すと+99円から+358円の幅があり、季節補正（-13円）よりはるかに大きい。第10期の単価をどの水準に置くかの判断に直結する。</t>
+          <t>令和8年度の単価の残差は＋1.63％であり、月額に直すと+99円である（分母は確認事項No.87の決着により一つに定まった）。季節補正（-13円）よりはるかに大きい。第10期の単価をどの水準に置くかの判断に直結する。</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
